--- a/artfynd/A 49079-2025 artfynd.xlsx
+++ b/artfynd/A 49079-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,49 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>89253811</v>
+        <v>128340280</v>
       </c>
       <c r="B2" t="n">
-        <v>95521</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92509</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>224363</v>
+        <v>760</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+          <t>Haploporus odorus</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Mellanström SV, Harrurvägen, SO Såppåive, Pi lm</t>
+          <t>Kallön, Pi lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>634977.713370165</v>
+        <v>634933</v>
       </c>
       <c r="R2" t="n">
-        <v>7299356.402709575</v>
+        <v>7299148</v>
       </c>
       <c r="S2" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -741,27 +744,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-08-16</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-08-16</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>491 m ö h.</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,74 +765,68 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>oskött' blandskog</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mats G Nettelbladt</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mats G Nettelbladt, Charlotte Nordgren</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>89253778</v>
+        <v>128340279</v>
       </c>
       <c r="B3" t="n">
-        <v>95524</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>224365</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Riplummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum subsp. monostachyon</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Grev. &amp; Hook.) Selander</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Mellanström SV, Harrurvägen, SO Såppåive, Pi lm</t>
+          <t>Kallön, Pi lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>634941.9727527042</v>
+        <v>634933</v>
       </c>
       <c r="R3" t="n">
-        <v>7299635.140274588</v>
+        <v>7299150</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -863,22 +850,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2020-08-16</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2020-08-16</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,21 +871,16 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>dikeszon</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mats G Nettelbladt</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mats G Nettelbladt, Charlotte Nordgren</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -913,12 +890,7 @@
         <v>89253773</v>
       </c>
       <c r="B4" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -950,10 +922,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>634941.9727527042</v>
+        <v>634942</v>
       </c>
       <c r="R4" t="n">
-        <v>7299635.140274588</v>
+        <v>7299635</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -983,19 +955,9 @@
           <t>2020-08-16</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-08-16</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,7 +982,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Mats G Nettelbladt, Charlotte Nordgren</t>
+          <t>Charlotte Nordgren, Mats G Nettelbladt</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1030,12 +992,7 @@
         <v>89253772</v>
       </c>
       <c r="B5" t="n">
-        <v>95526</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97990</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,10 +1020,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>634905.0071454213</v>
+        <v>634905</v>
       </c>
       <c r="R5" t="n">
-        <v>7299887.48205679</v>
+        <v>7299887</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1096,21 +1053,11 @@
           <t>2020-08-16</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2020-08-16</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1127,7 +1074,7 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>Pite lappmarks flora – herbarium FPLF</t>
+          <t>Umeå-Herbarium UME</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
@@ -1143,10 +1090,215 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Mats G Nettelbladt, Charlotte Nordgren</t>
+          <t>Charlotte Nordgren, Mats G Nettelbladt</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>89253811</v>
+      </c>
+      <c r="B6" t="n">
+        <v>97985</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>224363</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vanlig revlummer</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Mellanström SV, Harrurvägen, SO Såppåive, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>634978</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7299356</v>
+      </c>
+      <c r="S6" t="n">
+        <v>35</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2020-08-16</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2020-08-16</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>491 m ö h.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>oskött' blandskog</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Mats G Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Charlotte Nordgren, Mats G Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>89253778</v>
+      </c>
+      <c r="B7" t="n">
+        <v>97988</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>224365</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Riplummer</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum subsp. monostachyon</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Grev. &amp; Hook.) Selander</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Mellanström SV, Harrurvägen, SO Såppåive, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>634942</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7299635</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2020-08-16</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2020-08-16</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>dikeszon</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Mats G Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Charlotte Nordgren, Mats G Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 49079-2025 artfynd.xlsx
+++ b/artfynd/A 49079-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128340280</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128340279</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -986,6 +1001,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89253773</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1094,6 +1114,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89253772</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1197,6 +1222,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89253811</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1299,8 +1329,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89253778</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>